--- a/data/trans_orig/P79_n_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R2-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>793</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>310605</t>
+          <t>318040</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307109</t>
+          <t>314445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>284170</t>
+          <t>312627</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265426</t>
+          <t>298395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>594774</t>
+          <t>630667</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>574312</t>
+          <t>619823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600534</t>
+          <t>634113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39235</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>37051</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52992</t>
+          <t>55251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>498377</t>
+          <t>510950</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479155</t>
+          <t>494367</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>507469</t>
+          <t>519971</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>499356</t>
+          <t>529140</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>490103</t>
+          <t>520042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504981</t>
+          <t>535650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,22 +1251,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>997734</t>
+          <t>1040090</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>980367</t>
+          <t>1021890</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1009111</t>
+          <t>1051429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>16135</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>26049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>309232</t>
+          <t>308611</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300922</t>
+          <t>301084</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313018</t>
+          <t>312987</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>340664</t>
+          <t>347629</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333049</t>
+          <t>340435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>344748</t>
+          <t>352039</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>649896</t>
+          <t>656240</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640268</t>
+          <t>646326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656278</t>
+          <t>662695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>27047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>18681</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>308320</t>
+          <t>367627</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302352</t>
+          <t>360792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311372</t>
+          <t>371349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>463455</t>
+          <t>408798</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>450326</t>
+          <t>394914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470035</t>
+          <t>414804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>771774</t>
+          <t>776426</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>758949</t>
+          <t>762409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>779170</t>
+          <t>784206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>850</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177708</t>
+          <t>204531</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174962</t>
+          <t>201698</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>257987</t>
+          <t>228068</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>255911</t>
+          <t>225979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>435695</t>
+          <t>432598</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>433058</t>
+          <t>429326</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437078</t>
+          <t>434038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19198</t>
+          <t>22678</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>264679</t>
+          <t>264149</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257285</t>
+          <t>257556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267923</t>
+          <t>268096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>250959</t>
+          <t>256025</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244808</t>
+          <t>249451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253941</t>
+          <t>259792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>515638</t>
+          <t>520173</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507494</t>
+          <t>511779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520688</t>
+          <t>525942</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14590</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>14237</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>21609</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>32929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>616886</t>
+          <t>711293</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>609689</t>
+          <t>704576</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>621094</t>
+          <t>715618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>840796</t>
+          <t>757820</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>835086</t>
+          <t>750448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>846213</t>
+          <t>763309</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1457682</t>
+          <t>1469113</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1447836</t>
+          <t>1458815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1465057</t>
+          <t>1476402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>80805</t>
+          <t>97194</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>78809</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118317</t>
+          <t>116997</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>73182</t>
+          <t>85678</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59716</t>
+          <t>70476</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88639</t>
+          <t>104659</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>153987</t>
+          <t>182872</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>92389</t>
+          <t>158538</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>189400</t>
+          <t>207171</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>847915</t>
+          <t>700878</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>810403</t>
+          <t>681075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>894050</t>
+          <t>719263</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>644549</t>
+          <t>745653</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>629092</t>
+          <t>726672</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>658015</t>
+          <t>760855</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1492465</t>
+          <t>1446531</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1457052</t>
+          <t>1422232</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1554063</t>
+          <t>1470865</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,102 +3469,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>126095</t>
+          <t>146683</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>98439</t>
+          <t>122482</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>156452</t>
+          <t>177615</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>151194</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>130758</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>176427</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>297877</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>264928</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>335361</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>130345</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>102614</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>155967</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>256440</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>217030</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>298878</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -3582,102 +3582,102 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3333722</t>
+          <t>3386079</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3303365</t>
+          <t>3355147</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3361378</t>
+          <t>3410280</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5177</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3585760</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3560527</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3606196</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>8416</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6971839</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6934355</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>7004788</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>95,9%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>96,36%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>5177</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3581935</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3556313</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3609666</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>8416</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6915657</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6873219</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6955067</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
